--- a/research/traditional_assets/database/data/china/china_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.109</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="E2">
-        <v>0.144</v>
+        <v>-0.0568</v>
       </c>
       <c r="G2">
-        <v>0.05656758119227252</v>
+        <v>0.05932093460671607</v>
       </c>
       <c r="H2">
-        <v>0.05656758119227252</v>
+        <v>0.05932093460671607</v>
       </c>
       <c r="I2">
-        <v>0.06104052564573596</v>
+        <v>0.03203184537804225</v>
       </c>
       <c r="J2">
-        <v>0.048966818429215</v>
+        <v>0.02792508008512625</v>
       </c>
       <c r="K2">
-        <v>1123.4</v>
+        <v>602</v>
       </c>
       <c r="L2">
-        <v>0.04799336961815494</v>
+        <v>0.02440289916170772</v>
       </c>
       <c r="M2">
-        <v>288.3</v>
+        <v>260</v>
       </c>
       <c r="N2">
-        <v>0.07056145675265554</v>
+        <v>0.09641056066449125</v>
       </c>
       <c r="O2">
-        <v>0.2566316539077799</v>
+        <v>0.4318936877076412</v>
       </c>
       <c r="P2">
-        <v>288.3</v>
+        <v>260</v>
       </c>
       <c r="Q2">
-        <v>0.07056145675265554</v>
+        <v>0.09641056066449125</v>
       </c>
       <c r="R2">
-        <v>0.2566316539077799</v>
+        <v>0.4318936877076412</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2266.4</v>
+        <v>2120.1</v>
       </c>
       <c r="V2">
-        <v>0.5547016496157423</v>
+        <v>0.7861539602491842</v>
       </c>
       <c r="W2">
-        <v>0.09009254655396412</v>
+        <v>0.04140046352013974</v>
       </c>
       <c r="X2">
-        <v>0.1923490128396292</v>
+        <v>0.3163503110541603</v>
       </c>
       <c r="Y2">
-        <v>-0.1022564662856651</v>
+        <v>-0.2749498475340205</v>
       </c>
       <c r="Z2">
-        <v>1.304418574843826</v>
+        <v>1.18335100182761</v>
       </c>
       <c r="AA2">
-        <v>0.06387322751007302</v>
+        <v>0.03304517149485039</v>
       </c>
       <c r="AB2">
-        <v>0.07753390211385991</v>
+        <v>0.1074605877686615</v>
       </c>
       <c r="AC2">
-        <v>-0.01366067460378689</v>
+        <v>-0.07441541627381115</v>
       </c>
       <c r="AD2">
-        <v>8820.6</v>
+        <v>9198.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8820.6</v>
+        <v>9198.9</v>
       </c>
       <c r="AG2">
-        <v>6554.200000000001</v>
+        <v>7078.799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6834283766193516</v>
+        <v>0.7732962330926301</v>
       </c>
       <c r="AI2">
-        <v>0.3548095140405711</v>
+        <v>0.3856253537068478</v>
       </c>
       <c r="AJ2">
-        <v>0.6159962406015038</v>
+        <v>0.7241294651990671</v>
       </c>
       <c r="AK2">
-        <v>0.290089715274612</v>
+        <v>0.3256956713780918</v>
       </c>
       <c r="AL2">
-        <v>466.9</v>
+        <v>364.7</v>
       </c>
       <c r="AM2">
-        <v>466.9</v>
+        <v>364.7</v>
       </c>
       <c r="AN2">
-        <v>5.777559441933582</v>
+        <v>10.40481845945029</v>
       </c>
       <c r="AO2">
-        <v>3.060184193617477</v>
+        <v>2.166712366328489</v>
       </c>
       <c r="AP2">
-        <v>4.293050370079256</v>
+        <v>8.006786562606038</v>
       </c>
       <c r="AQ2">
-        <v>3.060184193617477</v>
+        <v>2.166712366328489</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.109</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="E3">
-        <v>0.144</v>
+        <v>-0.0568</v>
       </c>
       <c r="G3">
-        <v>0.05656758119227252</v>
+        <v>0.05932093460671607</v>
       </c>
       <c r="H3">
-        <v>0.05656758119227252</v>
+        <v>0.05932093460671607</v>
       </c>
       <c r="I3">
-        <v>0.06104052564573596</v>
+        <v>0.03203184537804225</v>
       </c>
       <c r="J3">
-        <v>0.048966818429215</v>
+        <v>0.02792508008512625</v>
       </c>
       <c r="K3">
-        <v>1123.4</v>
+        <v>602</v>
       </c>
       <c r="L3">
-        <v>0.04799336961815494</v>
+        <v>0.02440289916170772</v>
       </c>
       <c r="M3">
-        <v>288.3</v>
+        <v>260</v>
       </c>
       <c r="N3">
-        <v>0.07056145675265554</v>
+        <v>0.09641056066449125</v>
       </c>
       <c r="O3">
-        <v>0.2566316539077799</v>
+        <v>0.4318936877076412</v>
       </c>
       <c r="P3">
-        <v>288.3</v>
+        <v>260</v>
       </c>
       <c r="Q3">
-        <v>0.07056145675265554</v>
+        <v>0.09641056066449125</v>
       </c>
       <c r="R3">
-        <v>0.2566316539077799</v>
+        <v>0.4318936877076412</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2266.4</v>
+        <v>2120.1</v>
       </c>
       <c r="V3">
-        <v>0.5547016496157423</v>
+        <v>0.7861539602491842</v>
       </c>
       <c r="W3">
-        <v>0.09009254655396412</v>
+        <v>0.04140046352013974</v>
       </c>
       <c r="X3">
-        <v>0.1923490128396292</v>
+        <v>0.3163503110541603</v>
       </c>
       <c r="Y3">
-        <v>-0.1022564662856651</v>
+        <v>-0.2749498475340205</v>
       </c>
       <c r="Z3">
-        <v>1.304418574843826</v>
+        <v>1.18335100182761</v>
       </c>
       <c r="AA3">
-        <v>0.06387322751007302</v>
+        <v>0.03304517149485039</v>
       </c>
       <c r="AB3">
-        <v>0.07753390211385991</v>
+        <v>0.1074605877686615</v>
       </c>
       <c r="AC3">
-        <v>-0.01366067460378689</v>
+        <v>-0.07441541627381115</v>
       </c>
       <c r="AD3">
-        <v>8820.6</v>
+        <v>9198.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8820.6</v>
+        <v>9198.9</v>
       </c>
       <c r="AG3">
-        <v>6554.200000000001</v>
+        <v>7078.799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6834283766193516</v>
+        <v>0.7732962330926301</v>
       </c>
       <c r="AI3">
-        <v>0.3548095140405711</v>
+        <v>0.3856253537068478</v>
       </c>
       <c r="AJ3">
-        <v>0.6159962406015038</v>
+        <v>0.7241294651990671</v>
       </c>
       <c r="AK3">
-        <v>0.290089715274612</v>
+        <v>0.3256956713780918</v>
       </c>
       <c r="AL3">
-        <v>466.9</v>
+        <v>364.7</v>
       </c>
       <c r="AM3">
-        <v>466.9</v>
+        <v>364.7</v>
       </c>
       <c r="AN3">
-        <v>5.777559441933582</v>
+        <v>10.40481845945029</v>
       </c>
       <c r="AO3">
-        <v>3.060184193617477</v>
+        <v>2.166712366328489</v>
       </c>
       <c r="AP3">
-        <v>4.293050370079256</v>
+        <v>8.006786562606038</v>
       </c>
       <c r="AQ3">
-        <v>3.060184193617477</v>
+        <v>2.166712366328489</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08839999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="E2">
-        <v>-0.0568</v>
+        <v>-0.0591</v>
       </c>
       <c r="G2">
-        <v>0.05932093460671607</v>
+        <v>0.03302975356465837</v>
       </c>
       <c r="H2">
-        <v>0.05932093460671607</v>
+        <v>0.03302975356465837</v>
       </c>
       <c r="I2">
-        <v>0.03203184537804225</v>
+        <v>0.03738976345503997</v>
       </c>
       <c r="J2">
-        <v>0.02792508008512625</v>
+        <v>0.03738976345503997</v>
       </c>
       <c r="K2">
-        <v>602</v>
+        <v>471.1</v>
       </c>
       <c r="L2">
-        <v>0.02440289916170772</v>
+        <v>0.0194139948899695</v>
       </c>
       <c r="M2">
-        <v>260</v>
+        <v>263.6</v>
       </c>
       <c r="N2">
-        <v>0.09641056066449125</v>
+        <v>0.1065394875111147</v>
       </c>
       <c r="O2">
-        <v>0.4318936877076412</v>
+        <v>0.5595414986202505</v>
       </c>
       <c r="P2">
-        <v>260</v>
+        <v>263.6</v>
       </c>
       <c r="Q2">
-        <v>0.09641056066449125</v>
+        <v>0.1065394875111147</v>
       </c>
       <c r="R2">
-        <v>0.4318936877076412</v>
+        <v>0.5595414986202505</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2120.1</v>
+        <v>1474.5</v>
       </c>
       <c r="V2">
-        <v>0.7861539602491842</v>
+        <v>0.595950206127233</v>
       </c>
       <c r="W2">
-        <v>0.04140046352013974</v>
+        <v>0.03550353829573973</v>
       </c>
       <c r="X2">
-        <v>0.3163503110541603</v>
+        <v>0.2676179137096217</v>
       </c>
       <c r="Y2">
-        <v>-0.2749498475340205</v>
+        <v>-0.232114375413882</v>
       </c>
       <c r="Z2">
-        <v>1.18335100182761</v>
+        <v>1.206885404077329</v>
       </c>
       <c r="AA2">
-        <v>0.03304517149485039</v>
+        <v>0.04512515977579166</v>
       </c>
       <c r="AB2">
-        <v>0.1074605877686615</v>
+        <v>0.09043570226060829</v>
       </c>
       <c r="AC2">
-        <v>-0.07441541627381115</v>
+        <v>-0.04531054248481663</v>
       </c>
       <c r="AD2">
-        <v>9198.9</v>
+        <v>9222.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9198.9</v>
+        <v>9222.6</v>
       </c>
       <c r="AG2">
-        <v>7078.799999999999</v>
+        <v>7748.1</v>
       </c>
       <c r="AH2">
-        <v>0.7732962330926301</v>
+        <v>0.78847206073456</v>
       </c>
       <c r="AI2">
-        <v>0.3856253537068478</v>
+        <v>0.4001232136194435</v>
       </c>
       <c r="AJ2">
-        <v>0.7241294651990671</v>
+        <v>0.7579605372567818</v>
       </c>
       <c r="AK2">
-        <v>0.3256956713780918</v>
+        <v>0.3591256506403274</v>
       </c>
       <c r="AL2">
-        <v>364.7</v>
+        <v>415.6</v>
       </c>
       <c r="AM2">
-        <v>364.7</v>
+        <v>415.6</v>
       </c>
       <c r="AN2">
-        <v>10.40481845945029</v>
+        <v>9.204191616766467</v>
       </c>
       <c r="AO2">
-        <v>2.166712366328489</v>
+        <v>2.183108758421559</v>
       </c>
       <c r="AP2">
-        <v>8.006786562606038</v>
+        <v>7.732634730538923</v>
       </c>
       <c r="AQ2">
-        <v>2.166712366328489</v>
+        <v>2.183108758421559</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08839999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="E3">
-        <v>-0.0568</v>
+        <v>-0.0591</v>
       </c>
       <c r="G3">
-        <v>0.05932093460671607</v>
+        <v>0.03302975356465837</v>
       </c>
       <c r="H3">
-        <v>0.05932093460671607</v>
+        <v>0.03302975356465837</v>
       </c>
       <c r="I3">
-        <v>0.03203184537804225</v>
+        <v>0.03738976345503997</v>
       </c>
       <c r="J3">
-        <v>0.02792508008512625</v>
+        <v>0.03738976345503997</v>
       </c>
       <c r="K3">
-        <v>602</v>
+        <v>471.1</v>
       </c>
       <c r="L3">
-        <v>0.02440289916170772</v>
+        <v>0.0194139948899695</v>
       </c>
       <c r="M3">
-        <v>260</v>
+        <v>263.6</v>
       </c>
       <c r="N3">
-        <v>0.09641056066449125</v>
+        <v>0.1065394875111147</v>
       </c>
       <c r="O3">
-        <v>0.4318936877076412</v>
+        <v>0.5595414986202505</v>
       </c>
       <c r="P3">
-        <v>260</v>
+        <v>263.6</v>
       </c>
       <c r="Q3">
-        <v>0.09641056066449125</v>
+        <v>0.1065394875111147</v>
       </c>
       <c r="R3">
-        <v>0.4318936877076412</v>
+        <v>0.5595414986202505</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2120.1</v>
+        <v>1474.5</v>
       </c>
       <c r="V3">
-        <v>0.7861539602491842</v>
+        <v>0.595950206127233</v>
       </c>
       <c r="W3">
-        <v>0.04140046352013974</v>
+        <v>0.03550353829573973</v>
       </c>
       <c r="X3">
-        <v>0.3163503110541603</v>
+        <v>0.2676179137096217</v>
       </c>
       <c r="Y3">
-        <v>-0.2749498475340205</v>
+        <v>-0.232114375413882</v>
       </c>
       <c r="Z3">
-        <v>1.18335100182761</v>
+        <v>1.206885404077329</v>
       </c>
       <c r="AA3">
-        <v>0.03304517149485039</v>
+        <v>0.04512515977579166</v>
       </c>
       <c r="AB3">
-        <v>0.1074605877686615</v>
+        <v>0.09043570226060829</v>
       </c>
       <c r="AC3">
-        <v>-0.07441541627381115</v>
+        <v>-0.04531054248481663</v>
       </c>
       <c r="AD3">
-        <v>9198.9</v>
+        <v>9222.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9198.9</v>
+        <v>9222.6</v>
       </c>
       <c r="AG3">
-        <v>7078.799999999999</v>
+        <v>7748.1</v>
       </c>
       <c r="AH3">
-        <v>0.7732962330926301</v>
+        <v>0.78847206073456</v>
       </c>
       <c r="AI3">
-        <v>0.3856253537068478</v>
+        <v>0.4001232136194435</v>
       </c>
       <c r="AJ3">
-        <v>0.7241294651990671</v>
+        <v>0.7579605372567818</v>
       </c>
       <c r="AK3">
-        <v>0.3256956713780918</v>
+        <v>0.3591256506403274</v>
       </c>
       <c r="AL3">
-        <v>364.7</v>
+        <v>415.6</v>
       </c>
       <c r="AM3">
-        <v>364.7</v>
+        <v>415.6</v>
       </c>
       <c r="AN3">
-        <v>10.40481845945029</v>
+        <v>9.204191616766467</v>
       </c>
       <c r="AO3">
-        <v>2.166712366328489</v>
+        <v>2.183108758421559</v>
       </c>
       <c r="AP3">
-        <v>8.006786562606038</v>
+        <v>7.732634730538923</v>
       </c>
       <c r="AQ3">
-        <v>2.166712366328489</v>
+        <v>2.183108758421559</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>-0.0581</v>
       </c>
       <c r="E2">
-        <v>-0.0591</v>
+        <v>0.147</v>
       </c>
       <c r="G2">
-        <v>0.03302975356465837</v>
+        <v>0.06658380681818182</v>
       </c>
       <c r="H2">
-        <v>0.03302975356465837</v>
+        <v>0.06658380681818182</v>
       </c>
       <c r="I2">
-        <v>0.03738976345503997</v>
+        <v>0.1236292613636364</v>
       </c>
       <c r="J2">
-        <v>0.03738976345503997</v>
+        <v>0.1047970592590012</v>
       </c>
       <c r="K2">
-        <v>471.1</v>
+        <v>1289.1</v>
       </c>
       <c r="L2">
-        <v>0.0194139948899695</v>
+        <v>0.09155539772727272</v>
       </c>
       <c r="M2">
-        <v>263.6</v>
+        <v>81.8</v>
       </c>
       <c r="N2">
-        <v>0.1065394875111147</v>
+        <v>0.01719209751996637</v>
       </c>
       <c r="O2">
-        <v>0.5595414986202505</v>
+        <v>0.06345512372973393</v>
       </c>
       <c r="P2">
-        <v>263.6</v>
+        <v>81.8</v>
       </c>
       <c r="Q2">
-        <v>0.1065394875111147</v>
+        <v>0.01719209751996637</v>
       </c>
       <c r="R2">
-        <v>0.5595414986202505</v>
+        <v>0.06345512372973393</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1474.5</v>
+        <v>1726.7</v>
       </c>
       <c r="V2">
-        <v>0.595950206127233</v>
+        <v>0.3629045817570408</v>
       </c>
       <c r="W2">
-        <v>0.03550353829573973</v>
+        <v>0.1023818411417589</v>
       </c>
       <c r="X2">
-        <v>0.2676179137096217</v>
+        <v>0.1920223579507223</v>
       </c>
       <c r="Y2">
-        <v>-0.232114375413882</v>
+        <v>-0.08964051680896348</v>
       </c>
       <c r="Z2">
-        <v>1.206885404077329</v>
+        <v>0.7000969594510603</v>
       </c>
       <c r="AA2">
-        <v>0.04512515977579166</v>
+        <v>0.07336810254663934</v>
       </c>
       <c r="AB2">
-        <v>0.09043570226060829</v>
+        <v>0.0927784773413876</v>
       </c>
       <c r="AC2">
-        <v>-0.04531054248481663</v>
+        <v>-0.01941037479474826</v>
       </c>
       <c r="AD2">
-        <v>9222.6</v>
+        <v>10086.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9222.6</v>
+        <v>10086.5</v>
       </c>
       <c r="AG2">
-        <v>7748.1</v>
+        <v>8359.799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.78847206073456</v>
+        <v>0.6794772474653912</v>
       </c>
       <c r="AI2">
-        <v>0.4001232136194435</v>
+        <v>0.4054287620686052</v>
       </c>
       <c r="AJ2">
-        <v>0.7579605372567818</v>
+        <v>0.6372867401545991</v>
       </c>
       <c r="AK2">
-        <v>0.3591256506403274</v>
+        <v>0.3610848353698832</v>
       </c>
       <c r="AL2">
-        <v>415.6</v>
+        <v>309.3</v>
       </c>
       <c r="AM2">
-        <v>415.6</v>
+        <v>309.3</v>
       </c>
       <c r="AN2">
-        <v>9.204191616766467</v>
+        <v>5.528666959000219</v>
       </c>
       <c r="AO2">
-        <v>2.183108758421559</v>
+        <v>5.62786938247656</v>
       </c>
       <c r="AP2">
-        <v>7.732634730538923</v>
+        <v>4.582218811664108</v>
       </c>
       <c r="AQ2">
-        <v>2.183108758421559</v>
+        <v>5.62786938247656</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>-0.0581</v>
       </c>
       <c r="E3">
-        <v>-0.0591</v>
+        <v>0.147</v>
       </c>
       <c r="G3">
-        <v>0.03302975356465837</v>
+        <v>0.06658380681818182</v>
       </c>
       <c r="H3">
-        <v>0.03302975356465837</v>
+        <v>0.06658380681818182</v>
       </c>
       <c r="I3">
-        <v>0.03738976345503997</v>
+        <v>0.1236292613636364</v>
       </c>
       <c r="J3">
-        <v>0.03738976345503997</v>
+        <v>0.1047970592590012</v>
       </c>
       <c r="K3">
-        <v>471.1</v>
+        <v>1289.1</v>
       </c>
       <c r="L3">
-        <v>0.0194139948899695</v>
+        <v>0.09155539772727272</v>
       </c>
       <c r="M3">
-        <v>263.6</v>
+        <v>81.8</v>
       </c>
       <c r="N3">
-        <v>0.1065394875111147</v>
+        <v>0.01719209751996637</v>
       </c>
       <c r="O3">
-        <v>0.5595414986202505</v>
+        <v>0.06345512372973393</v>
       </c>
       <c r="P3">
-        <v>263.6</v>
+        <v>81.8</v>
       </c>
       <c r="Q3">
-        <v>0.1065394875111147</v>
+        <v>0.01719209751996637</v>
       </c>
       <c r="R3">
-        <v>0.5595414986202505</v>
+        <v>0.06345512372973393</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1474.5</v>
+        <v>1726.7</v>
       </c>
       <c r="V3">
-        <v>0.595950206127233</v>
+        <v>0.3629045817570408</v>
       </c>
       <c r="W3">
-        <v>0.03550353829573973</v>
+        <v>0.1023818411417589</v>
       </c>
       <c r="X3">
-        <v>0.2676179137096217</v>
+        <v>0.1920223579507223</v>
       </c>
       <c r="Y3">
-        <v>-0.232114375413882</v>
+        <v>-0.08964051680896348</v>
       </c>
       <c r="Z3">
-        <v>1.206885404077329</v>
+        <v>0.7000969594510603</v>
       </c>
       <c r="AA3">
-        <v>0.04512515977579166</v>
+        <v>0.07336810254663934</v>
       </c>
       <c r="AB3">
-        <v>0.09043570226060829</v>
+        <v>0.0927784773413876</v>
       </c>
       <c r="AC3">
-        <v>-0.04531054248481663</v>
+        <v>-0.01941037479474826</v>
       </c>
       <c r="AD3">
-        <v>9222.6</v>
+        <v>10086.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9222.6</v>
+        <v>10086.5</v>
       </c>
       <c r="AG3">
-        <v>7748.1</v>
+        <v>8359.799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.78847206073456</v>
+        <v>0.6794772474653912</v>
       </c>
       <c r="AI3">
-        <v>0.4001232136194435</v>
+        <v>0.4054287620686052</v>
       </c>
       <c r="AJ3">
-        <v>0.7579605372567818</v>
+        <v>0.6372867401545991</v>
       </c>
       <c r="AK3">
-        <v>0.3591256506403274</v>
+        <v>0.3610848353698832</v>
       </c>
       <c r="AL3">
-        <v>415.6</v>
+        <v>309.3</v>
       </c>
       <c r="AM3">
-        <v>415.6</v>
+        <v>309.3</v>
       </c>
       <c r="AN3">
-        <v>9.204191616766467</v>
+        <v>5.528666959000219</v>
       </c>
       <c r="AO3">
-        <v>2.183108758421559</v>
+        <v>5.62786938247656</v>
       </c>
       <c r="AP3">
-        <v>7.732634730538923</v>
+        <v>4.582218811664108</v>
       </c>
       <c r="AQ3">
-        <v>2.183108758421559</v>
+        <v>5.62786938247656</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/china/china_reinsurance.xlsx
@@ -645,10 +645,10 @@
         <v>0.1023818411417589</v>
       </c>
       <c r="X2">
-        <v>0.1920223579507223</v>
+        <v>0.19195779964129</v>
       </c>
       <c r="Y2">
-        <v>-0.08964051680896348</v>
+        <v>-0.08957595849953109</v>
       </c>
       <c r="Z2">
         <v>0.7000969594510603</v>
@@ -657,10 +657,10 @@
         <v>0.07336810254663934</v>
       </c>
       <c r="AB2">
-        <v>0.0927784773413876</v>
+        <v>0.09275778493434936</v>
       </c>
       <c r="AC2">
-        <v>-0.01941037479474826</v>
+        <v>-0.01938968238771002</v>
       </c>
       <c r="AD2">
         <v>10086.5</v>
@@ -779,10 +779,10 @@
         <v>0.1023818411417589</v>
       </c>
       <c r="X3">
-        <v>0.1920223579507223</v>
+        <v>0.19195779964129</v>
       </c>
       <c r="Y3">
-        <v>-0.08964051680896348</v>
+        <v>-0.08957595849953109</v>
       </c>
       <c r="Z3">
         <v>0.7000969594510603</v>
@@ -791,10 +791,10 @@
         <v>0.07336810254663934</v>
       </c>
       <c r="AB3">
-        <v>0.0927784773413876</v>
+        <v>0.09275778493434936</v>
       </c>
       <c r="AC3">
-        <v>-0.01941037479474826</v>
+        <v>-0.01938968238771002</v>
       </c>
       <c r="AD3">
         <v>10086.5</v>
